--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="242">
   <si>
     <t>Match</t>
   </si>
@@ -707,6 +707,45 @@
   </si>
   <si>
     <t>Fox Lodge 2nd XI v CI 2nd XI, The Lodge - 28 June 2026</t>
+  </si>
+  <si>
+    <t>Holywood Women 1st XI v Instonians Women 1st XI, Stormont - 19 July 2026</t>
+  </si>
+  <si>
+    <t>Lisburn 5th XI v Arches 2nd XI, Victoria Park - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Holywood 3rd XI v Downpatrick 3rd XI, TBC - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Enniskillen 1st XI v NIMACC 2nd XI, TBC - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Belfast Superkings 3rd XI v Amigos Belfast 2nd XI, City of Belfast Playing Fields (Amigos Belfast) - 19 July 2026</t>
+  </si>
+  <si>
+    <t>Lisburn 4th XI v Lisburn 3rd XI, Wallace Park - 19 July 2026</t>
+  </si>
+  <si>
+    <t>Woodvale 4th XI v CSNI 4th XI, Ballygomartin Road - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Downpatrick 2nd XI v Saintfield 2nd XI, TBC - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v Woodvale 2nd XI, Moylena - 17 July 2026</t>
+  </si>
+  <si>
+    <t>Cliftonville Academy 2nd XI v Lisburn 2nd XI, Castle Grounds - 17 July 2026</t>
+  </si>
+  <si>
+    <t>Waringstown 2nd XI v NCU Pathway XI, The Lawn - 17 July 2026</t>
+  </si>
+  <si>
+    <t>CSNI 2nd XI v CI 2nd XI, Stormont - 17 July 2026</t>
+  </si>
+  <si>
+    <t>Leinster 1st XI v CSNI 1st XI, Rathmines - 19 July 2026</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2633,6 +2672,102 @@
         <v>218</v>
       </c>
     </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>230</v>
+      </c>
+      <c r="B200" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>231</v>
+      </c>
+      <c r="B201" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>232</v>
+      </c>
+      <c r="B202" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>233</v>
+      </c>
+      <c r="B203" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>234</v>
+      </c>
+      <c r="B204" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>235</v>
+      </c>
+      <c r="B205" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>236</v>
+      </c>
+      <c r="B206" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>237</v>
+      </c>
+      <c r="B207" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>238</v>
+      </c>
+      <c r="B208" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>239</v>
+      </c>
+      <c r="B209" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>240</v>
+      </c>
+      <c r="B210" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>241</v>
+      </c>
+      <c r="B211" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2641,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.28515625" customWidth="1"/>
@@ -2760,6 +2895,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="243">
   <si>
     <t>Match</t>
   </si>
@@ -746,6 +746,9 @@
   </si>
   <si>
     <t>Leinster 1st XI v CSNI 1st XI, Rathmines - 19 July 2026</t>
+  </si>
+  <si>
+    <t>Bangor 3rd XI v Ardent Blues 3rd XI, TBC - 18 July 2026</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2730,15 +2733,15 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B207" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B208" t="s">
         <v>177</v>
@@ -2746,7 +2749,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B209" t="s">
         <v>177</v>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B210" t="s">
         <v>177</v>
@@ -2762,9 +2765,17 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>240</v>
+      </c>
+      <c r="B211" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>241</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
         <v>200</v>
       </c>
     </row>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="246">
   <si>
     <t>Match</t>
   </si>
@@ -749,6 +749,15 @@
   </si>
   <si>
     <t>Bangor 3rd XI v Ardent Blues 3rd XI, TBC - 18 July 2026</t>
+  </si>
+  <si>
+    <t>Laurelvale 2nd XI v CI 3rd XI, Belmont - 25 July 2026</t>
+  </si>
+  <si>
+    <t>Victoria 2nd XI v BISC 4th XI, TBC - 25 July 2026</t>
+  </si>
+  <si>
+    <t>Holywood 2nd XI v Dunmurry 4th XI, TBC - 25 July 2026</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2777,6 +2786,30 @@
       </c>
       <c r="B212" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>243</v>
+      </c>
+      <c r="B213" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>244</v>
+      </c>
+      <c r="B214" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>245</v>
+      </c>
+      <c r="B215" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="247">
   <si>
     <t>Match</t>
   </si>
@@ -758,6 +758,9 @@
   </si>
   <si>
     <t>Holywood 2nd XI v Dunmurry 4th XI, TBC - 25 July 2026</t>
+  </si>
+  <si>
+    <t>Lisburn 1st XI v Waringstown 1st XI, The Lawn - 26 July 2026</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B215"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2810,6 +2813,14 @@
       </c>
       <c r="B215" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>246</v>
+      </c>
+      <c r="B216" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="249">
   <si>
     <t>Match</t>
   </si>
@@ -761,6 +761,12 @@
   </si>
   <si>
     <t>Lisburn 1st XI v Waringstown 1st XI, The Lawn - 26 July 2026</t>
+  </si>
+  <si>
+    <t>Bangor Women 1st XI v Holywood Women 2nd XI, Upritchard Park - 27 July 2026</t>
+  </si>
+  <si>
+    <t>Lisburn Women 2nd XI v Bangor Women 2nd XI, TBC - 29 July 2026</t>
   </si>
 </sst>
 </file>
@@ -2831,7 +2837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.28515625" customWidth="1"/>
@@ -2958,6 +2964,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="251">
   <si>
     <t>Match</t>
   </si>
@@ -767,6 +767,12 @@
   </si>
   <si>
     <t>Lisburn Women 2nd XI v Bangor Women 2nd XI, TBC - 29 July 2026</t>
+  </si>
+  <si>
+    <t>Downpatrick 1st XI v Holywood 1st XI, The Meadow - 31 July 2026</t>
+  </si>
+  <si>
+    <t>Victoria 1st XI v Ards &amp; Donaghadee 1st XI, Northfield - 31 July 2026</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2827,6 +2833,22 @@
       </c>
       <c r="B216" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>249</v>
+      </c>
+      <c r="B217" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>250</v>
+      </c>
+      <c r="B218" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="256">
   <si>
     <t>Match</t>
   </si>
@@ -773,6 +773,21 @@
   </si>
   <si>
     <t>Victoria 1st XI v Ards &amp; Donaghadee 1st XI, Northfield - 31 July 2026</t>
+  </si>
+  <si>
+    <t>CI 2nd XI v Lisburn 2nd XI, Sandy Bay - 1 August 2026</t>
+  </si>
+  <si>
+    <t>Downpatrick 3rd XI v NIMACC 2nd XI, TBC - 1 August 2026</t>
+  </si>
+  <si>
+    <t>Arches 2nd XI v Amigos Belfast 2nd XI, TBC - 1 August 2026</t>
+  </si>
+  <si>
+    <t>Woodvale 4th XI v Downpatrick 2nd XI, The Meadow - 1 August 2026</t>
+  </si>
+  <si>
+    <t>Armagh 2nd XI v Ardent Blues 3rd XI, The Mall - 1 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B218"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2849,6 +2864,46 @@
       </c>
       <c r="B218" t="s">
         <v>170</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>251</v>
+      </c>
+      <c r="B219" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>255</v>
+      </c>
+      <c r="B220" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>254</v>
+      </c>
+      <c r="B221" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>252</v>
+      </c>
+      <c r="B222" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>253</v>
+      </c>
+      <c r="B223" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="257">
   <si>
     <t>Match</t>
   </si>
@@ -788,6 +788,9 @@
   </si>
   <si>
     <t>Armagh 2nd XI v Ardent Blues 3rd XI, The Mall - 1 August 2026</t>
+  </si>
+  <si>
+    <t>Instonians 1st XI v CSNI 1st XI, Stormont - 7 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2904,6 +2907,14 @@
       </c>
       <c r="B223" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>256</v>
+      </c>
+      <c r="B224" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="258">
   <si>
     <t>Match</t>
   </si>
@@ -791,6 +791,9 @@
   </si>
   <si>
     <t>Instonians 1st XI v CSNI 1st XI, Stormont - 7 August 2026</t>
+  </si>
+  <si>
+    <t>CI 3rd XI v Lisburn 4th XI, Queensway - 8 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2915,6 +2918,14 @@
       </c>
       <c r="B224" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>257</v>
+      </c>
+      <c r="B225" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="259">
   <si>
     <t>Match</t>
   </si>
@@ -794,6 +794,9 @@
   </si>
   <si>
     <t>CI 3rd XI v Lisburn 4th XI, Queensway - 8 August 2026</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v Brigade 2nd XI, Moylena - 9 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B225"/>
+  <dimension ref="A1:B226"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2926,6 +2929,14 @@
       </c>
       <c r="B225" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>258</v>
+      </c>
+      <c r="B226" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17B7CB8-6A7F-4AD0-B45A-3FC1E3E27411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="16155" yWindow="1590" windowWidth="22185" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="260">
   <si>
     <t>Match</t>
   </si>
@@ -797,12 +798,15 @@
   </si>
   <si>
     <t>Muckamore 2nd XI v Brigade 2nd XI, Moylena - 9 August 2026</t>
+  </si>
+  <si>
+    <t>Victoria 2nd XI v Holywood 2nd XI, The Mall - 15 August 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -840,10 +844,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,8 +1126,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B226"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2939,6 +2942,14 @@
         <v>218</v>
       </c>
     </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>259</v>
+      </c>
+      <c r="B227" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2946,7 +2957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2963,7 +2974,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -2987,7 +2998,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
@@ -2995,7 +3006,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
@@ -3003,7 +3014,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
@@ -3011,7 +3022,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
@@ -3019,7 +3030,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17B7CB8-6A7F-4AD0-B45A-3FC1E3E27411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AE2216-DC11-4E09-B974-A86403386188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16155" yWindow="1590" windowWidth="22185" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="261">
   <si>
     <t>Match</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Drumaness Superkings 1st XI v Downpatrick 1st XI, The Village Ground - 9 May 2026</t>
   </si>
   <si>
-    <t>Victoria 1st XI v Holywood 1881 1st XI, Lurgan Park - 9 May 2026</t>
-  </si>
-  <si>
     <t>Waringstown 2nd XI v Ballymena 1st XI, The Lawn - 10 May 2026</t>
   </si>
   <si>
@@ -287,9 +284,6 @@
     <t>Cooke Collegians 3rd XI v Belfast 2nd XI, TBC - 6 June 2026</t>
   </si>
   <si>
-    <t>Laurelvale 3rd XI v Holywood 1881 2nd XI, TBC - 6 June 2026</t>
-  </si>
-  <si>
     <t>Bangor 4th XI v Larne 2nd XI, TBC - 14 June 2026</t>
   </si>
   <si>
@@ -311,9 +305,6 @@
     <t>Belfast 2nd XI v Dunmurry 4th XI, TBC - 27 June 2026</t>
   </si>
   <si>
-    <t>Holywood 1881 2nd XI v CI 4th XI, Seapark Oval - 27 June 2026</t>
-  </si>
-  <si>
     <t>Ardent Blues 4th XI v Amigos Belfast 3rd XI, TBC - 9 May 2026</t>
   </si>
   <si>
@@ -353,9 +344,6 @@
     <t>Downpatrick 4th XI v Armagh 5th XI, TBC - 30 May 2026</t>
   </si>
   <si>
-    <t>Holywood 1881 3rd XI v Ards &amp; Donaghadee 3rd XI, TBC - 30 May 2026</t>
-  </si>
-  <si>
     <t>Lurgan 3rd XI v North Down 5th XI, TBC - 30 May 2026</t>
   </si>
   <si>
@@ -380,9 +368,6 @@
     <t>Amigos Belfast 2nd XI v Instonians 5th XI, TBC - 20 June 2026</t>
   </si>
   <si>
-    <t>Ballymena 3rd XI v Holywood 1881 3rd XI, TBC - 20 June 2026</t>
-  </si>
-  <si>
     <t>Bangor 5th XI v Enniskillen 1st XI, TBC - 20 June 2026</t>
   </si>
   <si>
@@ -521,9 +506,6 @@
     <t>Ballymena 1st XI v Larne 1st XI, Eaton Park - 25 June 2026</t>
   </si>
   <si>
-    <t>Holywood 1881 1st XI v BISC 1st XI, Seapark Oval - 25 June 2026</t>
-  </si>
-  <si>
     <t>Holywood 1st XI v Belfast 1st XI, Seapark Oval - 9 July 2026</t>
   </si>
   <si>
@@ -800,7 +782,28 @@
     <t>Muckamore 2nd XI v Brigade 2nd XI, Moylena - 9 August 2026</t>
   </si>
   <si>
+    <t>CSNI 1st XI v Pembroke 1st XI, Castle Avenue - 16 August 2026</t>
+  </si>
+  <si>
     <t>Victoria 2nd XI v Holywood 2nd XI, The Mall - 15 August 2026</t>
+  </si>
+  <si>
+    <t>Laurelvale 3rd XI v Holywood 2nd XI, TBC - 6 June 2026</t>
+  </si>
+  <si>
+    <t>Holywood 2nd XI v CI 4th XI, Seapark Oval - 27 June 2026</t>
+  </si>
+  <si>
+    <t>Holywood 3rd XI v Ards &amp; Donaghadee 3rd XI, TBC - 30 May 2026</t>
+  </si>
+  <si>
+    <t>Ballymena 3rd XI v Holywood 3rd XI, TBC - 20 June 2026</t>
+  </si>
+  <si>
+    <t>Holywood 1st XI v BISC 1st XI, Seapark Oval - 25 June 2026</t>
+  </si>
+  <si>
+    <t>Victoria 1st XI v Holywood 1st XI, Lurgan Park - 9 May 2026</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -1304,7 +1307,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -1312,7 +1315,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -1320,7 +1323,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -1328,7 +1331,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -1336,7 +1339,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -1344,7 +1347,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1352,7 +1355,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -1360,7 +1363,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -1368,7 +1371,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -1376,7 +1379,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1384,7 +1387,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -1392,7 +1395,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -1400,7 +1403,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>37</v>
@@ -1408,7 +1411,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1416,7 +1419,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -1424,7 +1427,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
         <v>37</v>
@@ -1432,7 +1435,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
@@ -1440,7 +1443,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
         <v>37</v>
@@ -1448,7 +1451,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" t="s">
         <v>37</v>
@@ -1456,1431 +1459,1431 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s">
         <v>71</v>
-      </c>
-      <c r="B53" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>255</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B108" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B113" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B122" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B123" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B124" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B125" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B126" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B128" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B129" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B130" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B132" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B136" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B139" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B140" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B141" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="B142" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B143" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B144" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B146" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B147" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B148" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B149" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B154" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B155" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B156" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B157" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B158" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B159" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B160" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B161" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B162" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B163" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B164" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B165" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B166" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>188</v>
+      </c>
+      <c r="B168" t="s">
         <v>194</v>
-      </c>
-      <c r="B168" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B169" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B170" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B171" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B173" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B174" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B175" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B176" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B177" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B178" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B179" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B180" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B181" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B182" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>204</v>
+      </c>
+      <c r="B183" t="s">
         <v>210</v>
-      </c>
-      <c r="B183" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B184" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B185" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B186" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B187" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B188" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B189" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B190" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B191" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B192" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B193" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B194" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B195" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B196" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B199" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B200" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B201" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B202" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B203" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B204" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B206" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B207" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B208" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B209" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B210" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B211" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B212" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B213" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B214" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B215" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B216" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B217" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B218" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B219" t="s">
         <v>37</v>
@@ -2888,39 +2891,39 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B220" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B221" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B222" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B223" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B224" t="s">
         <v>2</v>
@@ -2928,26 +2931,34 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B225" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B226" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B227" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>253</v>
+      </c>
+      <c r="B228" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +3090,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -3087,7 +3098,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -3095,7 +3106,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AE2216-DC11-4E09-B974-A86403386188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF03A0B-16A0-46C2-9CA0-0AB32218D558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="495" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="262">
   <si>
     <t>Match</t>
   </si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t>Victoria 1st XI v Holywood 1st XI, Lurgan Park - 9 May 2026</t>
+  </si>
+  <si>
+    <t>Downpatrick 2nd XI v Ardent Blues 3rd XI, The Meadow - 22 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B228"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2959,6 +2962,14 @@
       </c>
       <c r="B228" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>261</v>
+      </c>
+      <c r="B229" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF03A0B-16A0-46C2-9CA0-0AB32218D558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA396D-088D-4426-8CFF-5C9EE72630FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="495" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="267">
   <si>
     <t>Match</t>
   </si>
@@ -807,6 +807,21 @@
   </si>
   <si>
     <t>Downpatrick 2nd XI v Ardent Blues 3rd XI, The Meadow - 22 August 2026</t>
+  </si>
+  <si>
+    <t>Pembroke 1st XI v Lisburn 1st XI, The Lawn - 23 August 2026</t>
+  </si>
+  <si>
+    <t>Evara CI T20 Final</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v Fox Lodge 2nd XI, Ballygomartin Road - 23 August 2026</t>
+  </si>
+  <si>
+    <t>Merrion Women 1st XI v Holywood Women 1st XI, The Lawn - 23 August 2026</t>
+  </si>
+  <si>
+    <t>Evara Womens CI T20</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:B231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -2972,6 +2987,22 @@
         <v>71</v>
       </c>
     </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>262</v>
+      </c>
+      <c r="B230" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>264</v>
+      </c>
+      <c r="B231" t="s">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2980,7 +3011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.28515625" customWidth="1"/>
@@ -3123,6 +3154,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" t="s">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA396D-088D-4426-8CFF-5C9EE72630FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397AD181-7297-4F00-A98E-3697187A51E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2865" yWindow="1350" windowWidth="29655" windowHeight="19875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="268">
   <si>
     <t>Match</t>
   </si>
@@ -822,6 +822,9 @@
   </si>
   <si>
     <t>Evara Womens CI T20</t>
+  </si>
+  <si>
+    <t>Lisburn Women 2nd XI v Holywood Women 2nd XI, Seapark Oval - 24 August 2026</t>
   </si>
 </sst>
 </file>
@@ -3011,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75.28515625" customWidth="1"/>
@@ -3162,6 +3165,14 @@
         <v>266</v>
       </c>
     </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NCU_Cup_Fixtures.xlsx
+++ b/NCU_Cup_Fixtures.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397AD181-7297-4F00-A98E-3697187A51E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F333BDDB-92D5-423F-82ED-C2BB2FE5491C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="1350" windowWidth="29655" windowHeight="19875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10740" yWindow="810" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mens" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="270">
   <si>
     <t>Match</t>
   </si>
@@ -825,6 +825,12 @@
   </si>
   <si>
     <t>Lisburn Women 2nd XI v Holywood Women 2nd XI, Seapark Oval - 24 August 2026</t>
+  </si>
+  <si>
+    <t>Amigos Belfast 2nd XI v Downpatrick 3rd XI, The Meadow - 30 August 2026</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v CI 2nd XI, Moylena - 30 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B231"/>
+  <dimension ref="A1:B233"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77.7109375" customWidth="1"/>
@@ -3004,6 +3010,22 @@
       </c>
       <c r="B231" t="s">
         <v>212</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>268</v>
+      </c>
+      <c r="B232" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>269</v>
+      </c>
+      <c r="B233" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
